--- a/test-data/readexcel.xlsx
+++ b/test-data/readexcel.xlsx
@@ -1,46 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akshita Jain - 6768898\test-data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FA1768-7256-42EC-9F92-D4433CF106EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Sheet4" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>Akshita</t>
   </si>
+  <si>
+    <t>playwright</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -344,11 +337,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -356,4 +349,20 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
 </file>